--- a/ig/DM-DECEMBRE-2025/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/DM-DECEMBRE-2025/CodeSystem-terminologie-bdpm.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="101">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-11-06</t>
+    <t>2025-12-03</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-06T00:00:00+00:00</t>
+    <t>2025-12-03T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41206</t>
+    <t>41229</t>
   </si>
   <si>
     <t>Code</t>
@@ -146,18 +146,6 @@
   </si>
   <si>
     <t>code</t>
-  </si>
-  <si>
-    <t>etat_commercialisation</t>
-  </si>
-  <si>
-    <t>http://www.data.esante.gouv.fr/ANSM/BDPM-core-ontology/etat_commercialisation</t>
-  </si>
-  <si>
-    <t>statut_CIP</t>
-  </si>
-  <si>
-    <t>http://www.data.esante.gouv.fr/ANSM/BDPM-core-ontology/statut_CIP</t>
   </si>
   <si>
     <t>date_commercialisation</t>
@@ -640,7 +628,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -678,43 +666,43 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -726,7 +714,7 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -738,31 +726,31 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
@@ -774,7 +762,7 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
@@ -798,7 +786,7 @@
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>62</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
@@ -810,7 +798,7 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15">
@@ -822,7 +810,7 @@
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
@@ -834,7 +822,7 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
@@ -846,7 +834,7 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18">
@@ -870,7 +858,7 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
@@ -882,7 +870,7 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
@@ -894,7 +882,7 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22">
@@ -904,73 +892,49 @@
       <c r="B22" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="C22" s="2"/>
+      <c r="C22" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="D22" t="s" s="2">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>90</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>90</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>43</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="B25" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="D25" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="B26" s="2"/>
-      <c r="C26" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="D26" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -991,7 +955,7 @@
         <v>22</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -999,38 +963,38 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
